--- a/the analysis.xlsx
+++ b/the analysis.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\blaban analysis project\data_blaban\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\blaban analysis project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C18E0A3F-2F72-476A-AA57-387D422056D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5066BD7F-678F-4FC8-85AD-6CB31A7AD9D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="651" activeTab="4" xr2:uid="{AF6E0E80-9533-46E3-8E40-BD1348797296}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -670,20 +670,20 @@
   </cellStyleXfs>
   <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1354,8 +1354,8 @@
                         <a:cs typeface="+mn-cs"/>
                       </a:defRPr>
                     </a:pPr>
-                    <a:fld id="{A1575AC0-51BA-4F8A-B096-7B7986A986B1}" type="CELLRANGE">
-                      <a:rPr lang="en-US" sz="1200"/>
+                    <a:fld id="{9DD22C58-7ACA-4404-96E0-D4AB0042C557}" type="CELLRANGE">
+                      <a:rPr lang="en-US" sz="1200" baseline="0"/>
                       <a:pPr>
                         <a:defRPr sz="1200"/>
                       </a:pPr>
@@ -1366,7 +1366,7 @@
                       <a:t>
 </a:t>
                     </a:r>
-                    <a:fld id="{CDA61DEC-8323-4526-90CF-5D95FD233156}" type="CATEGORYNAME">
+                    <a:fld id="{DD118746-322A-4B7A-9CCA-6186724D97F9}" type="CATEGORYNAME">
                       <a:rPr lang="en-US" sz="1200" baseline="0"/>
                       <a:pPr>
                         <a:defRPr sz="1200"/>
@@ -1378,7 +1378,7 @@
                       <a:t>
 </a:t>
                     </a:r>
-                    <a:fld id="{007945D8-F827-42EF-BBB8-8391B7C235B5}" type="PERCENTAGE">
+                    <a:fld id="{9248FA02-AB90-4E9D-AD8B-374C9AE81266}" type="PERCENTAGE">
                       <a:rPr lang="en-US" sz="1200" baseline="0"/>
                       <a:pPr>
                         <a:defRPr sz="1200"/>
@@ -1457,8 +1457,8 @@
                         <a:cs typeface="+mn-cs"/>
                       </a:defRPr>
                     </a:pPr>
-                    <a:fld id="{94507ACC-602C-4C04-A089-FBB11C0E1773}" type="CELLRANGE">
-                      <a:rPr lang="en-US" sz="1200"/>
+                    <a:fld id="{36E1493B-3406-415B-8C65-F7F504EFB2CF}" type="CELLRANGE">
+                      <a:rPr lang="en-US" sz="1200" baseline="0"/>
                       <a:pPr>
                         <a:defRPr sz="1200"/>
                       </a:pPr>
@@ -1469,7 +1469,7 @@
                       <a:t>
 </a:t>
                     </a:r>
-                    <a:fld id="{F3415DD1-7219-4E33-A96C-BD26F4E740E4}" type="CATEGORYNAME">
+                    <a:fld id="{DEDEED83-E228-4B82-8221-9AC12C2520CD}" type="CATEGORYNAME">
                       <a:rPr lang="en-US" sz="1200" baseline="0"/>
                       <a:pPr>
                         <a:defRPr sz="1200"/>
@@ -1481,7 +1481,7 @@
                       <a:t>
 </a:t>
                     </a:r>
-                    <a:fld id="{00158077-DF11-4BBA-B1AB-811F9FAB6F4A}" type="PERCENTAGE">
+                    <a:fld id="{70D0E39C-ADBC-43A2-8E7F-A97F780FDB00}" type="PERCENTAGE">
                       <a:rPr lang="en-US" sz="1200" baseline="0"/>
                       <a:pPr>
                         <a:defRPr sz="1200"/>
@@ -2311,7 +2311,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{77866697-80C3-454F-B63B-85527C958150}" type="CELLRANGE">
+                    <a:fld id="{552E879C-DDF9-448A-AB96-829EE27DA5B5}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -2321,7 +2321,7 @@
                       <a:t>
 </a:t>
                     </a:r>
-                    <a:fld id="{CE3071B0-F37B-4A88-AB32-80B0DE359B25}" type="CATEGORYNAME">
+                    <a:fld id="{9A9446CA-4F54-40D6-A6AD-EEE6301F6186}" type="CATEGORYNAME">
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:pPr/>
                       <a:t>[CATEGORY NAME]</a:t>
@@ -2331,7 +2331,7 @@
                       <a:t>
 </a:t>
                     </a:r>
-                    <a:fld id="{F51AE031-63F9-4570-8FA4-26AA6D44CE11}" type="PERCENTAGE">
+                    <a:fld id="{FE718C27-B9DE-4429-AA81-B4D6A6FA050C}" type="PERCENTAGE">
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:pPr/>
                       <a:t>[PERCENTAGE]</a:t>
@@ -2365,7 +2365,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{68726E29-616B-403C-878B-11D95CAA49CE}" type="CELLRANGE">
+                    <a:fld id="{E2F0025A-1970-4890-9273-413A79AA7968}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -2375,7 +2375,7 @@
                       <a:t>
 </a:t>
                     </a:r>
-                    <a:fld id="{F4D85C7C-D529-48EE-BA3E-CE6614403AD6}" type="CATEGORYNAME">
+                    <a:fld id="{C52563E9-F28A-4DB4-9466-2B2951512DE1}" type="CATEGORYNAME">
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:pPr/>
                       <a:t>[CATEGORY NAME]</a:t>
@@ -2385,7 +2385,7 @@
                       <a:t>
 </a:t>
                     </a:r>
-                    <a:fld id="{32C95335-90D0-45FF-A24C-2A3B0607E399}" type="PERCENTAGE">
+                    <a:fld id="{0BF7A78B-8433-4935-A368-DE0D43B09CE7}" type="PERCENTAGE">
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:pPr/>
                       <a:t>[PERCENTAGE]</a:t>
@@ -2419,7 +2419,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{E70156EA-E4C5-4496-A4E7-288E2591F691}" type="CELLRANGE">
+                    <a:fld id="{3E59CE35-B8AF-452B-9469-FBDDCDE4779D}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -2429,7 +2429,7 @@
                       <a:t>
 </a:t>
                     </a:r>
-                    <a:fld id="{63D46CA4-BEAF-4993-92A6-EE3A7E68446A}" type="CATEGORYNAME">
+                    <a:fld id="{CFCF8E87-FCF8-4386-A2D7-B4BE25ECF4F4}" type="CATEGORYNAME">
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:pPr/>
                       <a:t>[CATEGORY NAME]</a:t>
@@ -2439,7 +2439,7 @@
                       <a:t>
 </a:t>
                     </a:r>
-                    <a:fld id="{22ECD196-E592-424F-8875-8922A457810B}" type="PERCENTAGE">
+                    <a:fld id="{61BDF4D8-EB35-4FAC-8B41-B46B30D8F8DA}" type="PERCENTAGE">
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:pPr/>
                       <a:t>[PERCENTAGE]</a:t>
@@ -2473,7 +2473,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{11A82CFA-3840-4D51-B660-4989CE3A4CA3}" type="CELLRANGE">
+                    <a:fld id="{BA1ABDAC-E270-495E-906E-76290F91F482}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -2483,7 +2483,7 @@
                       <a:t>
 </a:t>
                     </a:r>
-                    <a:fld id="{A1B65F6B-539F-4504-A0E6-CB0E7C3326DD}" type="CATEGORYNAME">
+                    <a:fld id="{D43E47F7-80F6-4341-8F7C-06C576070AFC}" type="CATEGORYNAME">
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:pPr/>
                       <a:t>[CATEGORY NAME]</a:t>
@@ -2493,7 +2493,7 @@
                       <a:t>
 </a:t>
                     </a:r>
-                    <a:fld id="{34A4A2DB-B87F-47B5-88CC-93F6ECEE5D22}" type="PERCENTAGE">
+                    <a:fld id="{220155C7-05C6-4A72-90C2-CC55F4077953}" type="PERCENTAGE">
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:pPr/>
                       <a:t>[PERCENTAGE]</a:t>
@@ -5513,38 +5513,38 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="2" t="s">
+      <c r="B1" s="6"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="2"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="2" t="s">
+      <c r="E1" s="6"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="H1" s="2"/>
-      <c r="I1" s="3"/>
-      <c r="J1" s="2" t="s">
+      <c r="H1" s="6"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="2"/>
-      <c r="L1" s="3"/>
-      <c r="M1" s="2" t="s">
+      <c r="K1" s="6"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="N1" s="2"/>
-      <c r="P1" s="2" t="s">
+      <c r="N1" s="6"/>
+      <c r="P1" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="Q1" s="2"/>
-      <c r="S1" s="1" t="s">
+      <c r="Q1" s="6"/>
+      <c r="S1" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="T1" s="1"/>
+      <c r="T1" s="5"/>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
@@ -5767,10 +5767,10 @@
       </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="2"/>
+      <c r="B8" s="6"/>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
@@ -5890,14 +5890,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="F1" s="2" t="s">
+      <c r="B1" s="6"/>
+      <c r="F1" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="G1" s="2"/>
+      <c r="G1" s="6"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
@@ -5920,13 +5920,13 @@
       <c r="B3">
         <v>2646</v>
       </c>
-      <c r="C3" s="6">
+      <c r="C3" s="3">
         <v>1960627.19</v>
       </c>
       <c r="F3" t="s">
         <v>25</v>
       </c>
-      <c r="G3" s="6">
+      <c r="G3" s="3">
         <v>2193014.6</v>
       </c>
     </row>
@@ -5937,13 +5937,13 @@
       <c r="B4">
         <v>1450</v>
       </c>
-      <c r="C4" s="6">
+      <c r="C4" s="3">
         <v>1066939.71</v>
       </c>
       <c r="F4" t="s">
         <v>24</v>
       </c>
-      <c r="G4" s="6">
+      <c r="G4" s="3">
         <v>2316115.0099999998</v>
       </c>
     </row>
@@ -5954,7 +5954,7 @@
       <c r="B5">
         <v>1413</v>
       </c>
-      <c r="C5" s="6">
+      <c r="C5" s="3">
         <v>1035473.56</v>
       </c>
     </row>
@@ -5965,7 +5965,7 @@
       <c r="B6">
         <v>671</v>
       </c>
-      <c r="C6" s="6">
+      <c r="C6" s="3">
         <v>478594.16</v>
       </c>
       <c r="F6" t="s">
@@ -6020,7 +6020,7 @@
       <c r="A2" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="6">
+      <c r="B2" s="3">
         <v>1583952.14</v>
       </c>
     </row>
@@ -6028,7 +6028,7 @@
       <c r="A3" t="s">
         <v>29</v>
       </c>
-      <c r="B3" s="6">
+      <c r="B3" s="3">
         <v>1477780.87</v>
       </c>
     </row>
@@ -6036,7 +6036,7 @@
       <c r="A4" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4" s="3">
         <v>1467898.66</v>
       </c>
     </row>
@@ -6044,7 +6044,7 @@
       <c r="A5" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="3">
         <v>602674.4</v>
       </c>
     </row>
@@ -6059,124 +6059,124 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="5:30" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="M1" s="5"/>
-      <c r="N1" s="5"/>
-      <c r="O1" s="5"/>
-      <c r="P1" s="5"/>
-      <c r="Q1" s="5"/>
-      <c r="R1" s="5"/>
-      <c r="S1" s="5"/>
-      <c r="T1" s="5"/>
-      <c r="U1" s="5"/>
-      <c r="V1" s="5"/>
-      <c r="W1" s="5"/>
-      <c r="X1" s="5"/>
-      <c r="Y1" s="5"/>
-      <c r="Z1" s="5"/>
-      <c r="AA1" s="5"/>
-      <c r="AB1" s="5"/>
-      <c r="AC1" s="5"/>
-      <c r="AD1" s="5"/>
+      <c r="M1" s="2"/>
+      <c r="N1" s="2"/>
+      <c r="O1" s="2"/>
+      <c r="P1" s="2"/>
+      <c r="Q1" s="2"/>
+      <c r="R1" s="2"/>
+      <c r="S1" s="2"/>
+      <c r="T1" s="2"/>
+      <c r="U1" s="2"/>
+      <c r="V1" s="2"/>
+      <c r="W1" s="2"/>
+      <c r="X1" s="2"/>
+      <c r="Y1" s="2"/>
+      <c r="Z1" s="2"/>
+      <c r="AA1" s="2"/>
+      <c r="AB1" s="2"/>
+      <c r="AC1" s="2"/>
+      <c r="AD1" s="2"/>
     </row>
     <row r="2" spans="5:30" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="M2" s="5"/>
-      <c r="N2" s="5"/>
-      <c r="O2" s="5"/>
-      <c r="P2" s="5"/>
-      <c r="Q2" s="5"/>
-      <c r="R2" s="5"/>
-      <c r="S2" s="5"/>
-      <c r="T2" s="5"/>
-      <c r="U2" s="5"/>
-      <c r="V2" s="5"/>
-      <c r="W2" s="5"/>
-      <c r="X2" s="5"/>
-      <c r="Y2" s="5"/>
-      <c r="Z2" s="5"/>
-      <c r="AA2" s="5"/>
-      <c r="AB2" s="5"/>
-      <c r="AC2" s="5"/>
-      <c r="AD2" s="5"/>
+      <c r="M2" s="2"/>
+      <c r="N2" s="2"/>
+      <c r="O2" s="2"/>
+      <c r="P2" s="2"/>
+      <c r="Q2" s="2"/>
+      <c r="R2" s="2"/>
+      <c r="S2" s="2"/>
+      <c r="T2" s="2"/>
+      <c r="U2" s="2"/>
+      <c r="V2" s="2"/>
+      <c r="W2" s="2"/>
+      <c r="X2" s="2"/>
+      <c r="Y2" s="2"/>
+      <c r="Z2" s="2"/>
+      <c r="AA2" s="2"/>
+      <c r="AB2" s="2"/>
+      <c r="AC2" s="2"/>
+      <c r="AD2" s="2"/>
     </row>
     <row r="3" spans="5:30" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="M3" s="5"/>
-      <c r="N3" s="5"/>
-      <c r="O3" s="5"/>
-      <c r="P3" s="5"/>
-      <c r="Q3" s="5"/>
-      <c r="R3" s="5"/>
-      <c r="S3" s="5"/>
-      <c r="T3" s="5"/>
-      <c r="U3" s="5"/>
-      <c r="V3" s="5"/>
-      <c r="W3" s="5"/>
-      <c r="X3" s="5"/>
-      <c r="Y3" s="5"/>
-      <c r="Z3" s="5"/>
-      <c r="AA3" s="5"/>
-      <c r="AB3" s="5"/>
-      <c r="AC3" s="5"/>
-      <c r="AD3" s="5"/>
+      <c r="M3" s="2"/>
+      <c r="N3" s="2"/>
+      <c r="O3" s="2"/>
+      <c r="P3" s="2"/>
+      <c r="Q3" s="2"/>
+      <c r="R3" s="2"/>
+      <c r="S3" s="2"/>
+      <c r="T3" s="2"/>
+      <c r="U3" s="2"/>
+      <c r="V3" s="2"/>
+      <c r="W3" s="2"/>
+      <c r="X3" s="2"/>
+      <c r="Y3" s="2"/>
+      <c r="Z3" s="2"/>
+      <c r="AA3" s="2"/>
+      <c r="AB3" s="2"/>
+      <c r="AC3" s="2"/>
+      <c r="AD3" s="2"/>
     </row>
     <row r="4" spans="5:30" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="M4" s="5"/>
-      <c r="N4" s="5"/>
-      <c r="O4" s="5"/>
-      <c r="P4" s="5"/>
-      <c r="Q4" s="5"/>
-      <c r="R4" s="5"/>
-      <c r="S4" s="5"/>
-      <c r="T4" s="5"/>
-      <c r="U4" s="5"/>
-      <c r="V4" s="5"/>
-      <c r="W4" s="5"/>
-      <c r="X4" s="5"/>
-      <c r="Y4" s="5"/>
-      <c r="Z4" s="5"/>
-      <c r="AA4" s="5"/>
-      <c r="AB4" s="5"/>
-      <c r="AC4" s="5"/>
-      <c r="AD4" s="5"/>
+      <c r="M4" s="2"/>
+      <c r="N4" s="2"/>
+      <c r="O4" s="2"/>
+      <c r="P4" s="2"/>
+      <c r="Q4" s="2"/>
+      <c r="R4" s="2"/>
+      <c r="S4" s="2"/>
+      <c r="T4" s="2"/>
+      <c r="U4" s="2"/>
+      <c r="V4" s="2"/>
+      <c r="W4" s="2"/>
+      <c r="X4" s="2"/>
+      <c r="Y4" s="2"/>
+      <c r="Z4" s="2"/>
+      <c r="AA4" s="2"/>
+      <c r="AB4" s="2"/>
+      <c r="AC4" s="2"/>
+      <c r="AD4" s="2"/>
     </row>
     <row r="5" spans="5:30" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="M5" s="5"/>
-      <c r="N5" s="5"/>
-      <c r="O5" s="5"/>
-      <c r="P5" s="5"/>
-      <c r="Q5" s="5"/>
-      <c r="R5" s="5"/>
-      <c r="S5" s="5"/>
-      <c r="T5" s="5"/>
-      <c r="U5" s="5"/>
-      <c r="V5" s="5"/>
-      <c r="W5" s="5"/>
-      <c r="X5" s="5"/>
-      <c r="Y5" s="5"/>
-      <c r="Z5" s="5"/>
-      <c r="AA5" s="5"/>
-      <c r="AB5" s="5"/>
-      <c r="AC5" s="5"/>
-      <c r="AD5" s="5"/>
+      <c r="M5" s="2"/>
+      <c r="N5" s="2"/>
+      <c r="O5" s="2"/>
+      <c r="P5" s="2"/>
+      <c r="Q5" s="2"/>
+      <c r="R5" s="2"/>
+      <c r="S5" s="2"/>
+      <c r="T5" s="2"/>
+      <c r="U5" s="2"/>
+      <c r="V5" s="2"/>
+      <c r="W5" s="2"/>
+      <c r="X5" s="2"/>
+      <c r="Y5" s="2"/>
+      <c r="Z5" s="2"/>
+      <c r="AA5" s="2"/>
+      <c r="AB5" s="2"/>
+      <c r="AC5" s="2"/>
+      <c r="AD5" s="2"/>
     </row>
     <row r="6" spans="5:30" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="M6" s="5"/>
-      <c r="N6" s="5"/>
-      <c r="O6" s="5"/>
-      <c r="P6" s="5"/>
-      <c r="Q6" s="5"/>
-      <c r="R6" s="5"/>
-      <c r="S6" s="5"/>
-      <c r="T6" s="5"/>
-      <c r="U6" s="5"/>
-      <c r="V6" s="5"/>
-      <c r="W6" s="5"/>
-      <c r="X6" s="5"/>
-      <c r="Y6" s="5"/>
-      <c r="Z6" s="5"/>
-      <c r="AA6" s="5"/>
-      <c r="AB6" s="5"/>
-      <c r="AC6" s="5"/>
-      <c r="AD6" s="5"/>
+      <c r="M6" s="2"/>
+      <c r="N6" s="2"/>
+      <c r="O6" s="2"/>
+      <c r="P6" s="2"/>
+      <c r="Q6" s="2"/>
+      <c r="R6" s="2"/>
+      <c r="S6" s="2"/>
+      <c r="T6" s="2"/>
+      <c r="U6" s="2"/>
+      <c r="V6" s="2"/>
+      <c r="W6" s="2"/>
+      <c r="X6" s="2"/>
+      <c r="Y6" s="2"/>
+      <c r="Z6" s="2"/>
+      <c r="AA6" s="2"/>
+      <c r="AB6" s="2"/>
+      <c r="AC6" s="2"/>
+      <c r="AD6" s="2"/>
     </row>
     <row r="7" spans="5:30" ht="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="8" spans="5:30" ht="14.4" customHeight="1" x14ac:dyDescent="0.3"/>

--- a/the analysis.xlsx
+++ b/the analysis.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\blaban analysis project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5066BD7F-678F-4FC8-85AD-6CB31A7AD9D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{750B2AC2-491C-433C-ABB4-2FF83F12F333}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="651" activeTab="4" xr2:uid="{AF6E0E80-9533-46E3-8E40-BD1348797296}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="651" firstSheet="4" activeTab="4" xr2:uid="{AF6E0E80-9533-46E3-8E40-BD1348797296}"/>
   </bookViews>
   <sheets>
-    <sheet name="riyadh &amp; dubai" sheetId="1" r:id="rId1"/>
-    <sheet name="colab branch sales" sheetId="13" r:id="rId2"/>
-    <sheet name="customer groups" sheetId="15" r:id="rId3"/>
-    <sheet name="sales per month" sheetId="17" r:id="rId4"/>
+    <sheet name="branches data" sheetId="1" state="hidden" r:id="rId1"/>
+    <sheet name="colab branch sales" sheetId="13" state="hidden" r:id="rId2"/>
+    <sheet name="customer groups" sheetId="15" state="hidden" r:id="rId3"/>
+    <sheet name="sales per month" sheetId="17" state="hidden" r:id="rId4"/>
     <sheet name="dashboard" sheetId="14" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
@@ -162,7 +162,7 @@
     <numFmt numFmtId="41" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -299,7 +299,7 @@
     </font>
     <font>
       <b/>
-      <sz val="28"/>
+      <sz val="32"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -307,8 +307,16 @@
     </font>
     <font>
       <b/>
-      <sz val="32"/>
+      <sz val="72"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="28"/>
+      <color theme="0"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -668,20 +676,24 @@
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="19" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -744,471 +756,6 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="en-US" sz="2400">
-                <a:solidFill>
-                  <a:schemeClr val="bg1"/>
-                </a:solidFill>
-              </a:rPr>
-              <a:t>Branch</a:t>
-            </a:r>
-            <a:r>
-              <a:rPr lang="en-US" sz="2400" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="bg1"/>
-                </a:solidFill>
-              </a:rPr>
-              <a:t> Sales</a:t>
-            </a:r>
-            <a:endParaRPr lang="en-US" sz="2400">
-              <a:solidFill>
-                <a:schemeClr val="bg1"/>
-              </a:solidFill>
-            </a:endParaRPr>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout/>
-      <c:lineChart>
-        <c:grouping val="stacked"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'colab branch sales'!$C$5</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>sum</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:gradFill>
-                <a:gsLst>
-                  <a:gs pos="0">
-                    <a:schemeClr val="accent1">
-                      <a:lumMod val="5000"/>
-                      <a:lumOff val="95000"/>
-                    </a:schemeClr>
-                  </a:gs>
-                  <a:gs pos="74000">
-                    <a:schemeClr val="accent1">
-                      <a:lumMod val="45000"/>
-                      <a:lumOff val="55000"/>
-                    </a:schemeClr>
-                  </a:gs>
-                  <a:gs pos="83000">
-                    <a:schemeClr val="accent1">
-                      <a:lumMod val="45000"/>
-                      <a:lumOff val="55000"/>
-                    </a:schemeClr>
-                  </a:gs>
-                  <a:gs pos="100000">
-                    <a:schemeClr val="accent1">
-                      <a:lumMod val="30000"/>
-                      <a:lumOff val="70000"/>
-                    </a:schemeClr>
-                  </a:gs>
-                </a:gsLst>
-                <a:lin ang="5400000" scaled="1"/>
-              </a:gradFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:val>
-            <c:numRef>
-              <c:f>'colab branch sales'!$C$6:$C$9</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>207055.84</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>173628.26</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>194999.94</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>68560.53</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-E94D-4A26-B334-FD3726896588}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:smooth val="0"/>
-        <c:axId val="672173120"/>
-        <c:axId val="672173600"/>
-      </c:lineChart>
-      <c:catAx>
-        <c:axId val="672173120"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="65000"/>
-                        <a:lumOff val="35000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="en-US" sz="1800">
-                    <a:solidFill>
-                      <a:schemeClr val="bg1"/>
-                    </a:solidFill>
-                  </a:rPr>
-                  <a:t>Month</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:solidFill>
-                <a:schemeClr val="bg1"/>
-              </a:solidFill>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="65000"/>
-                      <a:lumOff val="35000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-        </c:title>
-        <c:numFmt formatCode="0,\ &quot;k&quot;" sourceLinked="0"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="15000"/>
-                <a:lumOff val="85000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="bg1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="672173600"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="672173600"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-          <c:max val="250000"/>
-          <c:min val="0"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="65000"/>
-                        <a:lumOff val="35000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="en-US" sz="1800">
-                    <a:solidFill>
-                      <a:schemeClr val="bg1"/>
-                    </a:solidFill>
-                  </a:rPr>
-                  <a:t>Sales</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="65000"/>
-                      <a:lumOff val="35000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-        </c:title>
-        <c:numFmt formatCode="0,\ &quot;k&quot;" sourceLinked="0"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1"/>
-          </a:solidFill>
-          <a:ln>
-            <a:solidFill>
-              <a:schemeClr val="bg1"/>
-            </a:solidFill>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="bg1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="672173120"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-        <c:majorUnit val="50000"/>
-        <c:minorUnit val="10000"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="zero"/>
-    <c:showDLblsOverMax val="0"/>
-    <c:extLst>
-      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
-        <c16r3:dataDisplayOptions16>
-          <c16r3:dispNaAsBlank val="1"/>
-        </c16r3:dataDisplayOptions16>
-      </c:ext>
-    </c:extLst>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="accent1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="en-US"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-GB"/>
@@ -1345,7 +892,7 @@
                   <a:lstStyle/>
                   <a:p>
                     <a:pPr>
-                      <a:defRPr sz="1200" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:defRPr sz="8800" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                         <a:solidFill>
                           <a:schemeClr val="accent1"/>
                         </a:solidFill>
@@ -1354,38 +901,38 @@
                         <a:cs typeface="+mn-cs"/>
                       </a:defRPr>
                     </a:pPr>
-                    <a:fld id="{9DD22C58-7ACA-4404-96E0-D4AB0042C557}" type="CELLRANGE">
-                      <a:rPr lang="en-US" sz="1200" baseline="0"/>
+                    <a:fld id="{F0ECB0B1-EA23-45A3-9723-1E2D3491C618}" type="CELLRANGE">
+                      <a:rPr lang="en-US" sz="8800" baseline="0"/>
                       <a:pPr>
-                        <a:defRPr sz="1200"/>
+                        <a:defRPr sz="8800"/>
                       </a:pPr>
                       <a:t>[CELLRANGE]</a:t>
                     </a:fld>
                     <a:r>
-                      <a:rPr lang="en-US" sz="1200" baseline="0"/>
+                      <a:rPr lang="en-US" sz="8800" baseline="0"/>
                       <a:t>
 </a:t>
                     </a:r>
-                    <a:fld id="{DD118746-322A-4B7A-9CCA-6186724D97F9}" type="CATEGORYNAME">
-                      <a:rPr lang="en-US" sz="1200" baseline="0"/>
+                    <a:fld id="{3A8A5EAF-4A12-44E8-94DC-67A16D7CE376}" type="CATEGORYNAME">
+                      <a:rPr lang="en-US" sz="8800" baseline="0"/>
                       <a:pPr>
-                        <a:defRPr sz="1200"/>
+                        <a:defRPr sz="8800"/>
                       </a:pPr>
                       <a:t>[CATEGORY NAME]</a:t>
                     </a:fld>
                     <a:r>
-                      <a:rPr lang="en-US" sz="1200" baseline="0"/>
+                      <a:rPr lang="en-US" sz="8800" baseline="0"/>
                       <a:t>
 </a:t>
                     </a:r>
-                    <a:fld id="{9248FA02-AB90-4E9D-AD8B-374C9AE81266}" type="PERCENTAGE">
-                      <a:rPr lang="en-US" sz="1200" baseline="0"/>
+                    <a:fld id="{A4DA3992-EDDD-4F37-A483-C0589F544199}" type="PERCENTAGE">
+                      <a:rPr lang="en-US" sz="8800" baseline="0"/>
                       <a:pPr>
-                        <a:defRPr sz="1200"/>
+                        <a:defRPr sz="8800"/>
                       </a:pPr>
                       <a:t>[PERCENTAGE]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="en-US" sz="1200" baseline="0"/>
+                    <a:endParaRPr lang="en-US" sz="8800" baseline="0"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -1403,7 +950,7 @@
                 <a:lstStyle/>
                 <a:p>
                   <a:pPr>
-                    <a:defRPr sz="1200" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:defRPr sz="8800" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                       <a:solidFill>
                         <a:schemeClr val="accent1"/>
                       </a:solidFill>
@@ -1426,8 +973,8 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:layout>
                     <c:manualLayout>
-                      <c:w val="0.25589439267394037"/>
-                      <c:h val="0.2239704386551952"/>
+                      <c:w val="0.3111591870985666"/>
+                      <c:h val="0.30219870689519762"/>
                     </c:manualLayout>
                   </c15:layout>
                   <c15:dlblFieldTable/>
@@ -1448,7 +995,7 @@
                   <a:lstStyle/>
                   <a:p>
                     <a:pPr>
-                      <a:defRPr sz="1200" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:defRPr sz="8800" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                         <a:solidFill>
                           <a:schemeClr val="accent1"/>
                         </a:solidFill>
@@ -1457,38 +1004,38 @@
                         <a:cs typeface="+mn-cs"/>
                       </a:defRPr>
                     </a:pPr>
-                    <a:fld id="{36E1493B-3406-415B-8C65-F7F504EFB2CF}" type="CELLRANGE">
-                      <a:rPr lang="en-US" sz="1200" baseline="0"/>
+                    <a:fld id="{195FCEE1-CAF3-4083-8119-045B9DFBD483}" type="CELLRANGE">
+                      <a:rPr lang="en-US" sz="8800" baseline="0"/>
                       <a:pPr>
-                        <a:defRPr sz="1200"/>
+                        <a:defRPr sz="8800"/>
                       </a:pPr>
                       <a:t>[CELLRANGE]</a:t>
                     </a:fld>
                     <a:r>
-                      <a:rPr lang="en-US" sz="1200" baseline="0"/>
+                      <a:rPr lang="en-US" sz="8800" baseline="0"/>
                       <a:t>
 </a:t>
                     </a:r>
-                    <a:fld id="{DEDEED83-E228-4B82-8221-9AC12C2520CD}" type="CATEGORYNAME">
-                      <a:rPr lang="en-US" sz="1200" baseline="0"/>
+                    <a:fld id="{00BD1ED5-5616-4EEB-A1E0-62CC33CB6F81}" type="CATEGORYNAME">
+                      <a:rPr lang="en-US" sz="8800" baseline="0"/>
                       <a:pPr>
-                        <a:defRPr sz="1200"/>
+                        <a:defRPr sz="8800"/>
                       </a:pPr>
                       <a:t>[CATEGORY NAME]</a:t>
                     </a:fld>
                     <a:r>
-                      <a:rPr lang="en-US" sz="1200" baseline="0"/>
+                      <a:rPr lang="en-US" sz="8800" baseline="0"/>
                       <a:t>
 </a:t>
                     </a:r>
-                    <a:fld id="{70D0E39C-ADBC-43A2-8E7F-A97F780FDB00}" type="PERCENTAGE">
-                      <a:rPr lang="en-US" sz="1200" baseline="0"/>
+                    <a:fld id="{FA5E968B-BAB9-46C5-B382-CDA188A0D2B9}" type="PERCENTAGE">
+                      <a:rPr lang="en-US" sz="8800" baseline="0"/>
                       <a:pPr>
-                        <a:defRPr sz="1200"/>
+                        <a:defRPr sz="8800"/>
                       </a:pPr>
                       <a:t>[PERCENTAGE]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="en-US" sz="1200" baseline="0"/>
+                    <a:endParaRPr lang="en-US" sz="8800" baseline="0"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -1506,7 +1053,7 @@
                 <a:lstStyle/>
                 <a:p>
                   <a:pPr>
-                    <a:defRPr sz="1200" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:defRPr sz="8800" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                       <a:solidFill>
                         <a:schemeClr val="accent1"/>
                       </a:solidFill>
@@ -1529,8 +1076,8 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:layout>
                     <c:manualLayout>
-                      <c:w val="0.26814694183126409"/>
-                      <c:h val="0.20618231232756373"/>
+                      <c:w val="0.42139025381823964"/>
+                      <c:h val="0.31064668114373389"/>
                     </c:manualLayout>
                   </c15:layout>
                   <c15:dlblFieldTable/>
@@ -1555,7 +1102,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1200" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="8800" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:schemeClr val="accent1"/>
                     </a:solidFill>
@@ -1697,7 +1244,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-GB"/>
@@ -1987,7 +1534,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="all" spc="150" normalizeH="0" baseline="0">
+              <a:defRPr sz="6000" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="all" spc="150" normalizeH="0" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="lt1"/>
                 </a:solidFill>
@@ -2078,7 +1625,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="6000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="lt1"/>
                 </a:solidFill>
@@ -2136,7 +1683,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-GB"/>
@@ -2311,7 +1858,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{552E879C-DDF9-448A-AB96-829EE27DA5B5}" type="CELLRANGE">
+                    <a:fld id="{7E840B55-BABC-4A96-9DEC-A705B3FB27A4}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -2321,7 +1868,7 @@
                       <a:t>
 </a:t>
                     </a:r>
-                    <a:fld id="{9A9446CA-4F54-40D6-A6AD-EEE6301F6186}" type="CATEGORYNAME">
+                    <a:fld id="{C6B77EFA-A2F0-4FFA-9722-F95A620966F5}" type="CATEGORYNAME">
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:pPr/>
                       <a:t>[CATEGORY NAME]</a:t>
@@ -2331,7 +1878,7 @@
                       <a:t>
 </a:t>
                     </a:r>
-                    <a:fld id="{FE718C27-B9DE-4429-AA81-B4D6A6FA050C}" type="PERCENTAGE">
+                    <a:fld id="{A35BB73D-BA46-495B-AE36-22AECD032F6D}" type="PERCENTAGE">
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:pPr/>
                       <a:t>[PERCENTAGE]</a:t>
@@ -2365,7 +1912,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{E2F0025A-1970-4890-9273-413A79AA7968}" type="CELLRANGE">
+                    <a:fld id="{2D218E83-7EE5-4429-9BCE-ADE3456002DD}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -2375,7 +1922,7 @@
                       <a:t>
 </a:t>
                     </a:r>
-                    <a:fld id="{C52563E9-F28A-4DB4-9466-2B2951512DE1}" type="CATEGORYNAME">
+                    <a:fld id="{0A4EF3BE-BE56-433E-9385-0A543DFD742C}" type="CATEGORYNAME">
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:pPr/>
                       <a:t>[CATEGORY NAME]</a:t>
@@ -2385,7 +1932,7 @@
                       <a:t>
 </a:t>
                     </a:r>
-                    <a:fld id="{0BF7A78B-8433-4935-A368-DE0D43B09CE7}" type="PERCENTAGE">
+                    <a:fld id="{BDFB3183-7C47-419E-8192-591F6E1B3639}" type="PERCENTAGE">
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:pPr/>
                       <a:t>[PERCENTAGE]</a:t>
@@ -2419,7 +1966,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{3E59CE35-B8AF-452B-9469-FBDDCDE4779D}" type="CELLRANGE">
+                    <a:fld id="{D3BFA9B8-B4D6-4835-9D5B-428C2612A555}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -2429,7 +1976,7 @@
                       <a:t>
 </a:t>
                     </a:r>
-                    <a:fld id="{CFCF8E87-FCF8-4386-A2D7-B4BE25ECF4F4}" type="CATEGORYNAME">
+                    <a:fld id="{C1C51CA9-A60B-4C02-9CD5-AE964292574B}" type="CATEGORYNAME">
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:pPr/>
                       <a:t>[CATEGORY NAME]</a:t>
@@ -2439,7 +1986,7 @@
                       <a:t>
 </a:t>
                     </a:r>
-                    <a:fld id="{61BDF4D8-EB35-4FAC-8B41-B46B30D8F8DA}" type="PERCENTAGE">
+                    <a:fld id="{B8F7B606-41D2-4FFD-98AC-B8B5CD1CDD89}" type="PERCENTAGE">
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:pPr/>
                       <a:t>[PERCENTAGE]</a:t>
@@ -2473,7 +2020,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{BA1ABDAC-E270-495E-906E-76290F91F482}" type="CELLRANGE">
+                    <a:fld id="{C8BEDDCB-505F-49B8-B07A-DB8EE3B69FFF}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -2483,7 +2030,7 @@
                       <a:t>
 </a:t>
                     </a:r>
-                    <a:fld id="{D43E47F7-80F6-4341-8F7C-06C576070AFC}" type="CATEGORYNAME">
+                    <a:fld id="{F326FFE6-B68F-405B-B380-893613521120}" type="CATEGORYNAME">
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:pPr/>
                       <a:t>[CATEGORY NAME]</a:t>
@@ -2493,7 +2040,7 @@
                       <a:t>
 </a:t>
                     </a:r>
-                    <a:fld id="{220155C7-05C6-4A72-90C2-CC55F4077953}" type="PERCENTAGE">
+                    <a:fld id="{63249993-30F0-422D-96E9-F94B7FF174B6}" type="PERCENTAGE">
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:pPr/>
                       <a:t>[PERCENTAGE]</a:t>
@@ -2534,7 +2081,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="6600" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:schemeClr val="accent1"/>
                     </a:solidFill>
@@ -2652,6 +2199,341 @@
         </c:dLbls>
         <c:firstSliceAng val="0"/>
       </c:pieChart>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="accent1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="accent1"/>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-GB"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1500" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="all" spc="100" normalizeH="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>branch</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t>e sales</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1500" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="all" spc="100" normalizeH="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="8.8137754868759161E-2"/>
+          <c:y val="0.10581575534154378"/>
+          <c:w val="0.88708636503577076"/>
+          <c:h val="0.81807524655999508"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'colab branch sales'!$C$5</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>sum</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:pattFill prst="ltUpDiag">
+              <a:fgClr>
+                <a:schemeClr val="accent1"/>
+              </a:fgClr>
+              <a:bgClr>
+                <a:schemeClr val="lt1"/>
+              </a:bgClr>
+            </a:pattFill>
+            <a:ln>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:prstDash val="lgDashDot"/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="28575" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="lt1">
+                    <a:alpha val="50000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:cat>
+            <c:strRef>
+              <c:f>'colab branch sales'!$B$6:$B$9</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>January</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Febuary</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>March</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>April</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'colab branch sales'!$C$6:$C$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>207055.84</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>173628.26</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>194999.94</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>68560.53</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-6B08-4D97-8B70-804101238DF4}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="269"/>
+        <c:overlap val="-20"/>
+        <c:axId val="2048118480"/>
+        <c:axId val="2048120880"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="2048118480"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:alpha val="25000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="3175" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="accent1">
+                <a:lumMod val="60000"/>
+                <a:lumOff val="40000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="4400" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="all" spc="150" normalizeH="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="2048120880"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="2048120880"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="0,\ &quot;k&quot;" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="5400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="2048118480"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
       <c:spPr>
         <a:noFill/>
         <a:ln>
@@ -2855,522 +2737,6 @@
 </file>
 
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
-      <a:spAutoFit/>
-    </cs:bodyPr>
-  </cs:dataLabelCallout>
-  <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-    </cs:spPr>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-    </cs:spPr>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="28575" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="65000"/>
-          <a:lumOff val="35000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="75000"/>
-            <a:lumOff val="25000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:legend>
-  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:prstDash val="sysDot"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:wall>
-</cs:chartStyle>
-</file>
-
-<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="260">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -3894,7 +3260,7 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="214">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -4430,7 +3796,7 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="260">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -4555,6 +3921,542 @@
       <a:solidFill>
         <a:schemeClr val="phClr"/>
       </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:effectRef>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="34925" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+      <a:effectLst>
+        <a:outerShdw dist="25400" dir="2700000" algn="tl" rotWithShape="0">
+          <a:schemeClr val="phClr"/>
+        </a:outerShdw>
+      </a:effectLst>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="22225">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="35000"/>
+          <a:lumOff val="65000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+      <a:effectLst>
+        <a:glow rad="25400">
+          <a:schemeClr val="lt1"/>
+        </a:glow>
+      </a:effectLst>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:alpha val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:alpha val="10000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="3175" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+            <a:tint val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:defRPr sz="1500" b="1" kern="1200" cap="all" spc="100" normalizeH="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:alpha val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1">
+          <a:lumMod val="95000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="214">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" b="1" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="3175" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="800" kern="1200" cap="all" spc="150" normalizeH="0" baseline="0"/>
+  </cs:categoryAxis>
+  <cs:chartArea>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr">
+          <a:alpha val="70000"/>
+        </a:schemeClr>
+      </a:solidFill>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <cs:styleClr val="auto"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:pattFill prst="ltUpDiag">
+        <a:fgClr>
+          <a:schemeClr val="phClr"/>
+        </a:fgClr>
+        <a:bgClr>
+          <a:schemeClr val="lt1"/>
+        </a:bgClr>
+      </a:pattFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:pattFill prst="ltUpDiag">
+        <a:fgClr>
+          <a:schemeClr val="phClr"/>
+        </a:fgClr>
+        <a:bgClr>
+          <a:schemeClr val="lt1"/>
+        </a:bgClr>
+      </a:pattFill>
     </cs:spPr>
   </cs:dataPoint3D>
   <cs:dataPointLine>
@@ -4958,23 +4860,23 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>163285</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>11723</xdr:rowOff>
+      <xdr:col>99</xdr:col>
+      <xdr:colOff>326480</xdr:colOff>
+      <xdr:row>94</xdr:row>
+      <xdr:rowOff>76968</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>398318</xdr:colOff>
-      <xdr:row>47</xdr:row>
-      <xdr:rowOff>121227</xdr:rowOff>
+      <xdr:col>126</xdr:col>
+      <xdr:colOff>533400</xdr:colOff>
+      <xdr:row>182</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="4" name="Chart 3">
+        <xdr:cNvPr id="6" name="Chart 5">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C3FFD3EC-4BC6-46ED-9672-9B4584AF7125}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4F02919F-5D95-4151-82C9-2E174337C0EC}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4996,23 +4898,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>32</xdr:col>
-      <xdr:colOff>328391</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>57808</xdr:rowOff>
+      <xdr:col>43</xdr:col>
+      <xdr:colOff>152401</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>41</xdr:col>
-      <xdr:colOff>33792</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>129565</xdr:rowOff>
+      <xdr:col>98</xdr:col>
+      <xdr:colOff>367145</xdr:colOff>
+      <xdr:row>143</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="6" name="Chart 5">
+        <xdr:cNvPr id="7" name="Chart 6">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4F02919F-5D95-4151-82C9-2E174337C0EC}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00984AB2-B2F0-4B90-95EE-B9DBFC3857C6}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5034,23 +4936,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>3811</xdr:colOff>
-      <xdr:row>8</xdr:row>
+      <xdr:col>100</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>31</xdr:col>
-      <xdr:colOff>555496</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>126</xdr:col>
+      <xdr:colOff>118499</xdr:colOff>
+      <xdr:row>90</xdr:row>
+      <xdr:rowOff>37900</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="7" name="Chart 6">
+        <xdr:cNvPr id="8" name="Chart 7">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00984AB2-B2F0-4B90-95EE-B9DBFC3857C6}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{99D3B3E7-A475-4EDA-B3EA-1BF2CDD9B673}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5072,54 +4974,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>32</xdr:col>
-      <xdr:colOff>327417</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>78768</xdr:rowOff>
+      <xdr:col>51</xdr:col>
+      <xdr:colOff>151741</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>178128</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>41</xdr:col>
-      <xdr:colOff>7404</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>111926</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="8" name="Chart 7">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{99D3B3E7-A475-4EDA-B3EA-1BF2CDD9B673}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr>
-          <a:graphicFrameLocks/>
-        </xdr:cNvGraphicFramePr>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>502920</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>160020</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>29</xdr:col>
-      <xdr:colOff>60960</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>53340</xdr:rowOff>
+      <xdr:col>94</xdr:col>
+      <xdr:colOff>521196</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>138545</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -5134,8 +4998,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9037320" y="160020"/>
-          <a:ext cx="8702040" cy="1173480"/>
+          <a:off x="31947923" y="178128"/>
+          <a:ext cx="27178000" cy="3701144"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5174,19 +5038,57 @@
         <a:p>
           <a:pPr algn="ctr"/>
           <a:r>
-            <a:rPr lang="en-US" sz="4000" b="1"/>
+            <a:rPr lang="en-US" sz="9600" b="1"/>
             <a:t>B.Laban sales in the first third of 2024</a:t>
           </a:r>
         </a:p>
         <a:p>
           <a:pPr algn="ctr"/>
           <a:r>
-            <a:rPr lang="en-US" sz="4000" b="1"/>
+            <a:rPr lang="en-US" sz="9600" b="1"/>
             <a:t>Egypt, Riyadh &amp; Dubai</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>457201</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>41</xdr:col>
+      <xdr:colOff>287867</xdr:colOff>
+      <xdr:row>130</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1A6C79D8-1D9C-4F50-863B-797F8F9D2DA4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -5513,38 +5415,38 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="6"/>
+      <c r="B1" s="5"/>
       <c r="C1" s="1"/>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="6"/>
+      <c r="E1" s="5"/>
       <c r="F1" s="1"/>
-      <c r="G1" s="6" t="s">
+      <c r="G1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="H1" s="6"/>
+      <c r="H1" s="5"/>
       <c r="I1" s="1"/>
-      <c r="J1" s="6" t="s">
+      <c r="J1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="6"/>
+      <c r="K1" s="5"/>
       <c r="L1" s="1"/>
-      <c r="M1" s="6" t="s">
+      <c r="M1" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="N1" s="6"/>
-      <c r="P1" s="6" t="s">
+      <c r="N1" s="5"/>
+      <c r="P1" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="Q1" s="6"/>
-      <c r="S1" s="5" t="s">
+      <c r="Q1" s="5"/>
+      <c r="S1" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="T1" s="5"/>
+      <c r="T1" s="4"/>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
@@ -5767,10 +5669,10 @@
       </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="6"/>
+      <c r="B8" s="5"/>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
@@ -5830,12 +5732,12 @@
     <row r="5" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B5" t="str" cm="1">
         <f t="array" ref="B5:C9">_xlfn.IFS(
-dashboard!E9='riyadh &amp; dubai'!A9,'riyadh &amp; dubai'!A2:B6,
-dashboard!E9='riyadh &amp; dubai'!A10,'riyadh &amp; dubai'!D2:E6,
-dashboard!E9='riyadh &amp; dubai'!A11,'riyadh &amp; dubai'!G2:H6,
-dashboard!E9='riyadh &amp; dubai'!A12,'riyadh &amp; dubai'!J2:K6,
-dashboard!E9='riyadh &amp; dubai'!A13,'riyadh &amp; dubai'!M2:N6,
-dashboard!E9='riyadh &amp; dubai'!A14,'riyadh &amp; dubai'!P2:Q6,dashboard!E9='riyadh &amp; dubai'!A9,'riyadh &amp; dubai'!A2:B6,dashboard!E9='riyadh &amp; dubai'!A15,'riyadh &amp; dubai'!S2:T6)</f>
+dashboard!M9='branches data'!A9,'branches data'!A2:B6,
+dashboard!M9='branches data'!A10,'branches data'!D2:E6,
+dashboard!M9='branches data'!A11,'branches data'!G2:H6,
+dashboard!M9='branches data'!A12,'branches data'!J2:K6,
+dashboard!M9='branches data'!A13,'branches data'!M2:N6,
+dashboard!M9='branches data'!A14,'branches data'!P2:Q6,dashboard!M9='branches data'!A9,'branches data'!A2:B6,dashboard!M9='branches data'!A15,'branches data'!S2:T6)</f>
         <v>month</v>
       </c>
       <c r="C5" t="str">
@@ -5890,14 +5792,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="6"/>
-      <c r="F1" s="6" t="s">
+      <c r="B1" s="5"/>
+      <c r="F1" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="G1" s="6"/>
+      <c r="G1" s="5"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
@@ -6055,10 +5957,10 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD7619C9-43D7-4B73-84A8-96F042F1BA63}">
-  <dimension ref="E1:AD16"/>
+  <dimension ref="E1:AE22"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="5:30" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="5:31" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M1" s="2"/>
       <c r="N1" s="2"/>
       <c r="O1" s="2"/>
@@ -6078,7 +5980,7 @@
       <c r="AC1" s="2"/>
       <c r="AD1" s="2"/>
     </row>
-    <row r="2" spans="5:30" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="5:31" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M2" s="2"/>
       <c r="N2" s="2"/>
       <c r="O2" s="2"/>
@@ -6098,7 +6000,7 @@
       <c r="AC2" s="2"/>
       <c r="AD2" s="2"/>
     </row>
-    <row r="3" spans="5:30" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="5:31" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M3" s="2"/>
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
@@ -6118,7 +6020,7 @@
       <c r="AC3" s="2"/>
       <c r="AD3" s="2"/>
     </row>
-    <row r="4" spans="5:30" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="5:31" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M4" s="2"/>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -6138,7 +6040,7 @@
       <c r="AC4" s="2"/>
       <c r="AD4" s="2"/>
     </row>
-    <row r="5" spans="5:30" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="5:31" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M5" s="2"/>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -6158,7 +6060,7 @@
       <c r="AC5" s="2"/>
       <c r="AD5" s="2"/>
     </row>
-    <row r="6" spans="5:30" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="5:31" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M6" s="2"/>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
@@ -6178,42 +6080,347 @@
       <c r="AC6" s="2"/>
       <c r="AD6" s="2"/>
     </row>
-    <row r="7" spans="5:30" ht="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="8" spans="5:30" ht="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="9" spans="5:30" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E9" s="4" t="s">
+    <row r="7" spans="5:31" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E7" s="7"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="7"/>
+      <c r="I7" s="7"/>
+    </row>
+    <row r="8" spans="5:31" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E8" s="7"/>
+      <c r="F8" s="7"/>
+      <c r="G8" s="7"/>
+      <c r="H8" s="7"/>
+      <c r="I8" s="7"/>
+    </row>
+    <row r="9" spans="5:31" ht="14.4" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="E9" s="7"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8"/>
+      <c r="H9" s="8"/>
+      <c r="I9" s="8"/>
+      <c r="M9" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F9" s="4"/>
-      <c r="G9" s="4"/>
-      <c r="H9" s="4"/>
-      <c r="I9" s="4"/>
+      <c r="N9" s="6"/>
+      <c r="O9" s="6"/>
+      <c r="P9" s="6"/>
+      <c r="Q9" s="6"/>
+      <c r="R9" s="6"/>
+      <c r="S9" s="6"/>
+      <c r="T9" s="6"/>
+      <c r="U9" s="6"/>
+      <c r="V9" s="6"/>
+      <c r="W9" s="6"/>
+      <c r="X9" s="6"/>
+      <c r="Y9" s="6"/>
+      <c r="Z9" s="6"/>
+      <c r="AA9" s="6"/>
+      <c r="AB9" s="6"/>
+      <c r="AC9" s="6"/>
+      <c r="AD9" s="6"/>
+      <c r="AE9" s="6"/>
     </row>
-    <row r="10" spans="5:30" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
-      <c r="G10" s="4"/>
-      <c r="H10" s="4"/>
-      <c r="I10" s="4"/>
+    <row r="10" spans="5:31" ht="14.4" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="E10" s="8"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="8"/>
+      <c r="H10" s="8"/>
+      <c r="I10" s="8"/>
+      <c r="M10" s="6"/>
+      <c r="N10" s="6"/>
+      <c r="O10" s="6"/>
+      <c r="P10" s="6"/>
+      <c r="Q10" s="6"/>
+      <c r="R10" s="6"/>
+      <c r="S10" s="6"/>
+      <c r="T10" s="6"/>
+      <c r="U10" s="6"/>
+      <c r="V10" s="6"/>
+      <c r="W10" s="6"/>
+      <c r="X10" s="6"/>
+      <c r="Y10" s="6"/>
+      <c r="Z10" s="6"/>
+      <c r="AA10" s="6"/>
+      <c r="AB10" s="6"/>
+      <c r="AC10" s="6"/>
+      <c r="AD10" s="6"/>
+      <c r="AE10" s="6"/>
     </row>
-    <row r="11" spans="5:30" ht="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="12" spans="5:30" ht="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="15" spans="5:30" ht="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="16" spans="5:30" ht="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="11" spans="5:31" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E11" s="7"/>
+      <c r="F11" s="7"/>
+      <c r="G11" s="7"/>
+      <c r="H11" s="7"/>
+      <c r="I11" s="7"/>
+      <c r="M11" s="6"/>
+      <c r="N11" s="6"/>
+      <c r="O11" s="6"/>
+      <c r="P11" s="6"/>
+      <c r="Q11" s="6"/>
+      <c r="R11" s="6"/>
+      <c r="S11" s="6"/>
+      <c r="T11" s="6"/>
+      <c r="U11" s="6"/>
+      <c r="V11" s="6"/>
+      <c r="W11" s="6"/>
+      <c r="X11" s="6"/>
+      <c r="Y11" s="6"/>
+      <c r="Z11" s="6"/>
+      <c r="AA11" s="6"/>
+      <c r="AB11" s="6"/>
+      <c r="AC11" s="6"/>
+      <c r="AD11" s="6"/>
+      <c r="AE11" s="6"/>
+    </row>
+    <row r="12" spans="5:31" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M12" s="6"/>
+      <c r="N12" s="6"/>
+      <c r="O12" s="6"/>
+      <c r="P12" s="6"/>
+      <c r="Q12" s="6"/>
+      <c r="R12" s="6"/>
+      <c r="S12" s="6"/>
+      <c r="T12" s="6"/>
+      <c r="U12" s="6"/>
+      <c r="V12" s="6"/>
+      <c r="W12" s="6"/>
+      <c r="X12" s="6"/>
+      <c r="Y12" s="6"/>
+      <c r="Z12" s="6"/>
+      <c r="AA12" s="6"/>
+      <c r="AB12" s="6"/>
+      <c r="AC12" s="6"/>
+      <c r="AD12" s="6"/>
+      <c r="AE12" s="6"/>
+    </row>
+    <row r="13" spans="5:31" x14ac:dyDescent="0.3">
+      <c r="M13" s="6"/>
+      <c r="N13" s="6"/>
+      <c r="O13" s="6"/>
+      <c r="P13" s="6"/>
+      <c r="Q13" s="6"/>
+      <c r="R13" s="6"/>
+      <c r="S13" s="6"/>
+      <c r="T13" s="6"/>
+      <c r="U13" s="6"/>
+      <c r="V13" s="6"/>
+      <c r="W13" s="6"/>
+      <c r="X13" s="6"/>
+      <c r="Y13" s="6"/>
+      <c r="Z13" s="6"/>
+      <c r="AA13" s="6"/>
+      <c r="AB13" s="6"/>
+      <c r="AC13" s="6"/>
+      <c r="AD13" s="6"/>
+      <c r="AE13" s="6"/>
+    </row>
+    <row r="14" spans="5:31" x14ac:dyDescent="0.3">
+      <c r="M14" s="6"/>
+      <c r="N14" s="6"/>
+      <c r="O14" s="6"/>
+      <c r="P14" s="6"/>
+      <c r="Q14" s="6"/>
+      <c r="R14" s="6"/>
+      <c r="S14" s="6"/>
+      <c r="T14" s="6"/>
+      <c r="U14" s="6"/>
+      <c r="V14" s="6"/>
+      <c r="W14" s="6"/>
+      <c r="X14" s="6"/>
+      <c r="Y14" s="6"/>
+      <c r="Z14" s="6"/>
+      <c r="AA14" s="6"/>
+      <c r="AB14" s="6"/>
+      <c r="AC14" s="6"/>
+      <c r="AD14" s="6"/>
+      <c r="AE14" s="6"/>
+    </row>
+    <row r="15" spans="5:31" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M15" s="6"/>
+      <c r="N15" s="6"/>
+      <c r="O15" s="6"/>
+      <c r="P15" s="6"/>
+      <c r="Q15" s="6"/>
+      <c r="R15" s="6"/>
+      <c r="S15" s="6"/>
+      <c r="T15" s="6"/>
+      <c r="U15" s="6"/>
+      <c r="V15" s="6"/>
+      <c r="W15" s="6"/>
+      <c r="X15" s="6"/>
+      <c r="Y15" s="6"/>
+      <c r="Z15" s="6"/>
+      <c r="AA15" s="6"/>
+      <c r="AB15" s="6"/>
+      <c r="AC15" s="6"/>
+      <c r="AD15" s="6"/>
+      <c r="AE15" s="6"/>
+    </row>
+    <row r="16" spans="5:31" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M16" s="6"/>
+      <c r="N16" s="6"/>
+      <c r="O16" s="6"/>
+      <c r="P16" s="6"/>
+      <c r="Q16" s="6"/>
+      <c r="R16" s="6"/>
+      <c r="S16" s="6"/>
+      <c r="T16" s="6"/>
+      <c r="U16" s="6"/>
+      <c r="V16" s="6"/>
+      <c r="W16" s="6"/>
+      <c r="X16" s="6"/>
+      <c r="Y16" s="6"/>
+      <c r="Z16" s="6"/>
+      <c r="AA16" s="6"/>
+      <c r="AB16" s="6"/>
+      <c r="AC16" s="6"/>
+      <c r="AD16" s="6"/>
+      <c r="AE16" s="6"/>
+    </row>
+    <row r="17" spans="13:31" x14ac:dyDescent="0.3">
+      <c r="M17" s="6"/>
+      <c r="N17" s="6"/>
+      <c r="O17" s="6"/>
+      <c r="P17" s="6"/>
+      <c r="Q17" s="6"/>
+      <c r="R17" s="6"/>
+      <c r="S17" s="6"/>
+      <c r="T17" s="6"/>
+      <c r="U17" s="6"/>
+      <c r="V17" s="6"/>
+      <c r="W17" s="6"/>
+      <c r="X17" s="6"/>
+      <c r="Y17" s="6"/>
+      <c r="Z17" s="6"/>
+      <c r="AA17" s="6"/>
+      <c r="AB17" s="6"/>
+      <c r="AC17" s="6"/>
+      <c r="AD17" s="6"/>
+      <c r="AE17" s="6"/>
+    </row>
+    <row r="18" spans="13:31" x14ac:dyDescent="0.3">
+      <c r="M18" s="6"/>
+      <c r="N18" s="6"/>
+      <c r="O18" s="6"/>
+      <c r="P18" s="6"/>
+      <c r="Q18" s="6"/>
+      <c r="R18" s="6"/>
+      <c r="S18" s="6"/>
+      <c r="T18" s="6"/>
+      <c r="U18" s="6"/>
+      <c r="V18" s="6"/>
+      <c r="W18" s="6"/>
+      <c r="X18" s="6"/>
+      <c r="Y18" s="6"/>
+      <c r="Z18" s="6"/>
+      <c r="AA18" s="6"/>
+      <c r="AB18" s="6"/>
+      <c r="AC18" s="6"/>
+      <c r="AD18" s="6"/>
+      <c r="AE18" s="6"/>
+    </row>
+    <row r="19" spans="13:31" x14ac:dyDescent="0.3">
+      <c r="M19" s="6"/>
+      <c r="N19" s="6"/>
+      <c r="O19" s="6"/>
+      <c r="P19" s="6"/>
+      <c r="Q19" s="6"/>
+      <c r="R19" s="6"/>
+      <c r="S19" s="6"/>
+      <c r="T19" s="6"/>
+      <c r="U19" s="6"/>
+      <c r="V19" s="6"/>
+      <c r="W19" s="6"/>
+      <c r="X19" s="6"/>
+      <c r="Y19" s="6"/>
+      <c r="Z19" s="6"/>
+      <c r="AA19" s="6"/>
+      <c r="AB19" s="6"/>
+      <c r="AC19" s="6"/>
+      <c r="AD19" s="6"/>
+      <c r="AE19" s="6"/>
+    </row>
+    <row r="20" spans="13:31" x14ac:dyDescent="0.3">
+      <c r="M20" s="6"/>
+      <c r="N20" s="6"/>
+      <c r="O20" s="6"/>
+      <c r="P20" s="6"/>
+      <c r="Q20" s="6"/>
+      <c r="R20" s="6"/>
+      <c r="S20" s="6"/>
+      <c r="T20" s="6"/>
+      <c r="U20" s="6"/>
+      <c r="V20" s="6"/>
+      <c r="W20" s="6"/>
+      <c r="X20" s="6"/>
+      <c r="Y20" s="6"/>
+      <c r="Z20" s="6"/>
+      <c r="AA20" s="6"/>
+      <c r="AB20" s="6"/>
+      <c r="AC20" s="6"/>
+      <c r="AD20" s="6"/>
+      <c r="AE20" s="6"/>
+    </row>
+    <row r="21" spans="13:31" x14ac:dyDescent="0.3">
+      <c r="M21" s="6"/>
+      <c r="N21" s="6"/>
+      <c r="O21" s="6"/>
+      <c r="P21" s="6"/>
+      <c r="Q21" s="6"/>
+      <c r="R21" s="6"/>
+      <c r="S21" s="6"/>
+      <c r="T21" s="6"/>
+      <c r="U21" s="6"/>
+      <c r="V21" s="6"/>
+      <c r="W21" s="6"/>
+      <c r="X21" s="6"/>
+      <c r="Y21" s="6"/>
+      <c r="Z21" s="6"/>
+      <c r="AA21" s="6"/>
+      <c r="AB21" s="6"/>
+      <c r="AC21" s="6"/>
+      <c r="AD21" s="6"/>
+      <c r="AE21" s="6"/>
+    </row>
+    <row r="22" spans="13:31" x14ac:dyDescent="0.3">
+      <c r="M22" s="6"/>
+      <c r="N22" s="6"/>
+      <c r="O22" s="6"/>
+      <c r="P22" s="6"/>
+      <c r="Q22" s="6"/>
+      <c r="R22" s="6"/>
+      <c r="S22" s="6"/>
+      <c r="T22" s="6"/>
+      <c r="U22" s="6"/>
+      <c r="V22" s="6"/>
+      <c r="W22" s="6"/>
+      <c r="X22" s="6"/>
+      <c r="Y22" s="6"/>
+      <c r="Z22" s="6"/>
+      <c r="AA22" s="6"/>
+      <c r="AB22" s="6"/>
+      <c r="AC22" s="6"/>
+      <c r="AD22" s="6"/>
+      <c r="AE22" s="6"/>
+    </row>
   </sheetData>
+  <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
-    <mergeCell ref="E9:I10"/>
+    <mergeCell ref="M9:AE22"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{5970621B-8C82-4809-B334-A11E374661C5}">
           <x14:formula1>
-            <xm:f>'riyadh &amp; dubai'!$A$9:$A$15</xm:f>
+            <xm:f>'branches data'!$A$9:$A$15</xm:f>
           </x14:formula1>
-          <xm:sqref>E9:I10</xm:sqref>
+          <xm:sqref>E10:I10 F9:I9 M9</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/the analysis.xlsx
+++ b/the analysis.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\blaban analysis project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{750B2AC2-491C-433C-ABB4-2FF83F12F333}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA990522-7BB2-46A2-88B7-F2DE5A11708C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="651" firstSheet="4" activeTab="4" xr2:uid="{AF6E0E80-9533-46E3-8E40-BD1348797296}"/>
   </bookViews>
@@ -683,17 +683,17 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -901,7 +901,7 @@
                         <a:cs typeface="+mn-cs"/>
                       </a:defRPr>
                     </a:pPr>
-                    <a:fld id="{F0ECB0B1-EA23-45A3-9723-1E2D3491C618}" type="CELLRANGE">
+                    <a:fld id="{6F42DC48-5F6E-40BD-853F-C4A48F6905E0}" type="CELLRANGE">
                       <a:rPr lang="en-US" sz="8800" baseline="0"/>
                       <a:pPr>
                         <a:defRPr sz="8800"/>
@@ -913,7 +913,7 @@
                       <a:t>
 </a:t>
                     </a:r>
-                    <a:fld id="{3A8A5EAF-4A12-44E8-94DC-67A16D7CE376}" type="CATEGORYNAME">
+                    <a:fld id="{6CC53D64-FB64-46A4-A6D5-6EA8A0DD5DE3}" type="CATEGORYNAME">
                       <a:rPr lang="en-US" sz="8800" baseline="0"/>
                       <a:pPr>
                         <a:defRPr sz="8800"/>
@@ -925,7 +925,7 @@
                       <a:t>
 </a:t>
                     </a:r>
-                    <a:fld id="{A4DA3992-EDDD-4F37-A483-C0589F544199}" type="PERCENTAGE">
+                    <a:fld id="{CACF5000-2CEF-4B20-8DBD-D629215B8ACA}" type="PERCENTAGE">
                       <a:rPr lang="en-US" sz="8800" baseline="0"/>
                       <a:pPr>
                         <a:defRPr sz="8800"/>
@@ -1004,7 +1004,7 @@
                         <a:cs typeface="+mn-cs"/>
                       </a:defRPr>
                     </a:pPr>
-                    <a:fld id="{195FCEE1-CAF3-4083-8119-045B9DFBD483}" type="CELLRANGE">
+                    <a:fld id="{277970C0-2334-4953-A21B-DCF2B806D5D4}" type="CELLRANGE">
                       <a:rPr lang="en-US" sz="8800" baseline="0"/>
                       <a:pPr>
                         <a:defRPr sz="8800"/>
@@ -1016,7 +1016,7 @@
                       <a:t>
 </a:t>
                     </a:r>
-                    <a:fld id="{00BD1ED5-5616-4EEB-A1E0-62CC33CB6F81}" type="CATEGORYNAME">
+                    <a:fld id="{BC2604EA-86C9-40AB-A00C-306714E1E905}" type="CATEGORYNAME">
                       <a:rPr lang="en-US" sz="8800" baseline="0"/>
                       <a:pPr>
                         <a:defRPr sz="8800"/>
@@ -1028,7 +1028,7 @@
                       <a:t>
 </a:t>
                     </a:r>
-                    <a:fld id="{FA5E968B-BAB9-46C5-B382-CDA188A0D2B9}" type="PERCENTAGE">
+                    <a:fld id="{FD847E1B-9D20-4479-91D6-2728E27B8A5D}" type="PERCENTAGE">
                       <a:rPr lang="en-US" sz="8800" baseline="0"/>
                       <a:pPr>
                         <a:defRPr sz="8800"/>
@@ -1858,7 +1858,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{7E840B55-BABC-4A96-9DEC-A705B3FB27A4}" type="CELLRANGE">
+                    <a:fld id="{440852BE-651B-4C58-8501-A9C9D0A4CEA6}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -1868,7 +1868,7 @@
                       <a:t>
 </a:t>
                     </a:r>
-                    <a:fld id="{C6B77EFA-A2F0-4FFA-9722-F95A620966F5}" type="CATEGORYNAME">
+                    <a:fld id="{FC7E37D4-5C30-4E8A-B31C-F30D905E6ECA}" type="CATEGORYNAME">
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:pPr/>
                       <a:t>[CATEGORY NAME]</a:t>
@@ -1878,7 +1878,7 @@
                       <a:t>
 </a:t>
                     </a:r>
-                    <a:fld id="{A35BB73D-BA46-495B-AE36-22AECD032F6D}" type="PERCENTAGE">
+                    <a:fld id="{49604924-FFD7-47FC-BDF1-65A7C65460B5}" type="PERCENTAGE">
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:pPr/>
                       <a:t>[PERCENTAGE]</a:t>
@@ -1912,7 +1912,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{2D218E83-7EE5-4429-9BCE-ADE3456002DD}" type="CELLRANGE">
+                    <a:fld id="{E9CA110C-1FF9-40AF-ABE5-431973E617A8}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -1922,7 +1922,7 @@
                       <a:t>
 </a:t>
                     </a:r>
-                    <a:fld id="{0A4EF3BE-BE56-433E-9385-0A543DFD742C}" type="CATEGORYNAME">
+                    <a:fld id="{B3C9B6C5-17F2-45D9-AEA9-2E05AAE21012}" type="CATEGORYNAME">
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:pPr/>
                       <a:t>[CATEGORY NAME]</a:t>
@@ -1932,7 +1932,7 @@
                       <a:t>
 </a:t>
                     </a:r>
-                    <a:fld id="{BDFB3183-7C47-419E-8192-591F6E1B3639}" type="PERCENTAGE">
+                    <a:fld id="{B2B2E67C-952A-4AC5-A699-3E95F3A99F00}" type="PERCENTAGE">
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:pPr/>
                       <a:t>[PERCENTAGE]</a:t>
@@ -1966,7 +1966,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{D3BFA9B8-B4D6-4835-9D5B-428C2612A555}" type="CELLRANGE">
+                    <a:fld id="{63C7035C-D074-4583-9F84-3EB835E09FE0}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -1976,7 +1976,7 @@
                       <a:t>
 </a:t>
                     </a:r>
-                    <a:fld id="{C1C51CA9-A60B-4C02-9CD5-AE964292574B}" type="CATEGORYNAME">
+                    <a:fld id="{C93177C6-213B-434B-9C69-BEAB5DA64B12}" type="CATEGORYNAME">
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:pPr/>
                       <a:t>[CATEGORY NAME]</a:t>
@@ -1986,7 +1986,7 @@
                       <a:t>
 </a:t>
                     </a:r>
-                    <a:fld id="{B8F7B606-41D2-4FFD-98AC-B8B5CD1CDD89}" type="PERCENTAGE">
+                    <a:fld id="{B3B32AE2-F96E-47FD-95FC-519A94B1547B}" type="PERCENTAGE">
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:pPr/>
                       <a:t>[PERCENTAGE]</a:t>
@@ -2020,7 +2020,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{C8BEDDCB-505F-49B8-B07A-DB8EE3B69FFF}" type="CELLRANGE">
+                    <a:fld id="{35A05AFA-9D3A-43AF-BAB0-7ED41BD6E87F}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -2030,7 +2030,7 @@
                       <a:t>
 </a:t>
                     </a:r>
-                    <a:fld id="{F326FFE6-B68F-405B-B380-893613521120}" type="CATEGORYNAME">
+                    <a:fld id="{DF831E6E-748A-45CF-BC99-947B9DA5EF61}" type="CATEGORYNAME">
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:pPr/>
                       <a:t>[CATEGORY NAME]</a:t>
@@ -2040,7 +2040,7 @@
                       <a:t>
 </a:t>
                     </a:r>
-                    <a:fld id="{63249993-30F0-422D-96E9-F94B7FF174B6}" type="PERCENTAGE">
+                    <a:fld id="{74DD75DA-5D36-4426-81E6-9E58E30B2B1A}" type="PERCENTAGE">
                       <a:rPr lang="en-US" baseline="0"/>
                       <a:pPr/>
                       <a:t>[PERCENTAGE]</a:t>
@@ -5415,38 +5415,38 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="5"/>
+      <c r="B1" s="8"/>
       <c r="C1" s="1"/>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="5"/>
+      <c r="E1" s="8"/>
       <c r="F1" s="1"/>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="H1" s="5"/>
+      <c r="H1" s="8"/>
       <c r="I1" s="1"/>
-      <c r="J1" s="5" t="s">
+      <c r="J1" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="5"/>
+      <c r="K1" s="8"/>
       <c r="L1" s="1"/>
-      <c r="M1" s="5" t="s">
+      <c r="M1" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="N1" s="5"/>
-      <c r="P1" s="5" t="s">
+      <c r="N1" s="8"/>
+      <c r="P1" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="Q1" s="5"/>
-      <c r="S1" s="4" t="s">
+      <c r="Q1" s="8"/>
+      <c r="S1" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="T1" s="4"/>
+      <c r="T1" s="7"/>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
@@ -5669,10 +5669,10 @@
       </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="5"/>
+      <c r="B8" s="8"/>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
@@ -5792,14 +5792,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="F1" s="5" t="s">
+      <c r="B1" s="8"/>
+      <c r="F1" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="G1" s="5"/>
+      <c r="G1" s="8"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
@@ -6081,25 +6081,25 @@
       <c r="AD6" s="2"/>
     </row>
     <row r="7" spans="5:31" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E7" s="7"/>
-      <c r="F7" s="7"/>
-      <c r="G7" s="7"/>
-      <c r="H7" s="7"/>
-      <c r="I7" s="7"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4"/>
     </row>
     <row r="8" spans="5:31" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
-      <c r="G8" s="7"/>
-      <c r="H8" s="7"/>
-      <c r="I8" s="7"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4"/>
+      <c r="I8" s="4"/>
     </row>
     <row r="9" spans="5:31" ht="14.4" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="E9" s="7"/>
-      <c r="F9" s="8"/>
-      <c r="G9" s="8"/>
-      <c r="H9" s="8"/>
-      <c r="I9" s="8"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="5"/>
+      <c r="H9" s="5"/>
+      <c r="I9" s="5"/>
       <c r="M9" s="6" t="s">
         <v>13</v>
       </c>
@@ -6123,11 +6123,11 @@
       <c r="AE9" s="6"/>
     </row>
     <row r="10" spans="5:31" ht="14.4" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
-      <c r="H10" s="8"/>
-      <c r="I10" s="8"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="5"/>
+      <c r="G10" s="5"/>
+      <c r="H10" s="5"/>
+      <c r="I10" s="5"/>
       <c r="M10" s="6"/>
       <c r="N10" s="6"/>
       <c r="O10" s="6"/>
@@ -6149,11 +6149,11 @@
       <c r="AE10" s="6"/>
     </row>
     <row r="11" spans="5:31" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
-      <c r="G11" s="7"/>
-      <c r="H11" s="7"/>
-      <c r="I11" s="7"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
+      <c r="G11" s="4"/>
+      <c r="H11" s="4"/>
+      <c r="I11" s="4"/>
       <c r="M11" s="6"/>
       <c r="N11" s="6"/>
       <c r="O11" s="6"/>
@@ -6406,7 +6406,6 @@
       <c r="AE22" s="6"/>
     </row>
   </sheetData>
-  <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="M9:AE22"/>
   </mergeCells>
